--- a/artfynd/A 28929-2022 artfynd.xlsx
+++ b/artfynd/A 28929-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28929-2022 artfynd.xlsx
+++ b/artfynd/A 28929-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40131</v>
+        <v>6824504</v>
       </c>
       <c r="B2" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,61 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>100069</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Hyla arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Johanneslust., Sk</t>
+          <t>65-104 Johanneslust norra., Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433404.830853086</v>
+        <v>433405</v>
       </c>
       <c r="R2" t="n">
-        <v>6170319.905785985</v>
+        <v>6170320</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1985-03-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1985-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,19 +792,18 @@
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6824504</v>
+        <v>40131</v>
       </c>
       <c r="B3" t="n">
-        <v>57558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,61 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100069</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hyla arborea</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>65-104 Johanneslust norra., Sk</t>
+          <t>N Johanneslust., Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433404.830853086</v>
+        <v>433405</v>
       </c>
       <c r="R3" t="n">
-        <v>6170319.905785985</v>
+        <v>6170320</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-03-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-03-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,11 +893,7 @@
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
